--- a/EKG_Kalite_Yönetim_Sistemi/15_Katmanlı Denetim ve Yetkinlik/02_LPASK3 - Eğitim ve Operatör Yeterliliği/EKG-IK-MTR-01_egitim_yetkinlik_ve_lojistik_ilu_matrisi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/15_Katmanlı Denetim ve Yetkinlik/02_LPASK3 - Eğitim ve Operatör Yeterliliği/EKG-IK-MTR-01_egitim_yetkinlik_ve_lojistik_ilu_matrisi.xlsx
@@ -792,7 +792,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-IK-MTR-01&amp;C&amp;"Arial,Regular"&amp;11Eğitim, Yetkinlik ve Lojistik ILU Matrisi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 03.06.2026 | Revizyon: 07.09.2026
+Revizyon nedeni: Yüzdesel skor çıkarıldı; operasyon bazlı I/L/U, kanıt/onay ve gerçek yasal belge takibi kuruldu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -944,7 +945,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-IK-MTR-01&amp;C&amp;"Arial,Regular"&amp;11Eğitim, Yetkinlik ve Lojistik ILU Matrisi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 03.06.2026 | Revizyon: 07.09.2026
+Revizyon nedeni: Yüzdesel skor çıkarıldı; operasyon bazlı I/L/U, kanıt/onay ve gerçek yasal belge takibi kuruldu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>